--- a/src/evaluation/data/processed/RES_deprivation_aware_model.xlsx
+++ b/src/evaluation/data/processed/RES_deprivation_aware_model.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.466</v>
+        <v>17.468</v>
       </c>
       <c r="C2" t="n">
         <v>12.08</v>
@@ -481,10 +481,10 @@
         <v>28.85</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8389044640931638</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3284823284823285</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.686</v>
+        <v>15.46</v>
       </c>
       <c r="C3" t="n">
-        <v>9.98</v>
+        <v>17.27</v>
       </c>
       <c r="D3" t="n">
-        <v>10.57</v>
+        <v>19.48</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.6416845110635259</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09584086799276677</v>
+        <v>0.8679833679833681</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.2729671011793918</v>
       </c>
     </row>
     <row r="4">
@@ -531,13 +531,13 @@
         <v>23.792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2935087340953202</v>
+        <v>0.09707351891506046</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7233041575492342</v>
+        <v>0.6075418994413407</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.412</v>
+        <v>17.094</v>
       </c>
       <c r="C5" t="n">
         <v>15.68</v>
@@ -556,13 +556,13 @@
         <v>27.038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7252533965926243</v>
+        <v>0.933261955745896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6112115732368897</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="G5" t="n">
-        <v>0.900875273522976</v>
+        <v>0.8594040968342646</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.96</v>
+        <v>16.7</v>
       </c>
       <c r="C6" t="n">
-        <v>19.98</v>
+        <v>18.54</v>
       </c>
       <c r="D6" t="n">
-        <v>25.286</v>
+        <v>20.964</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.8629550321199142</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8050328227571117</v>
+        <v>0.3881129733085043</v>
       </c>
     </row>
     <row r="7">
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.172</v>
+        <v>11.864</v>
       </c>
       <c r="C7" t="n">
-        <v>12.69</v>
+        <v>11.4</v>
       </c>
       <c r="D7" t="n">
-        <v>22.75</v>
+        <v>15.962</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4837179210696571</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3408679927667269</v>
+        <v>0.2577962577962579</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6663019693654267</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
